--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -781,7 +781,7 @@
         <v>117830856</v>
       </c>
       <c r="B3" t="n">
-        <v>97740</v>
+        <v>97742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353597</v>
+        <v>121353608</v>
       </c>
       <c r="B4" t="n">
-        <v>105161</v>
+        <v>97991</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353557</v>
+        <v>121357128</v>
       </c>
       <c r="B5" t="n">
-        <v>97025</v>
+        <v>97991</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>223572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R5" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353622</v>
+        <v>121353597</v>
       </c>
       <c r="B6" t="n">
-        <v>97084</v>
+        <v>105171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221063</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121357128</v>
+        <v>121353557</v>
       </c>
       <c r="B7" t="n">
-        <v>97981</v>
+        <v>97035</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R7" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353608</v>
+        <v>121353620</v>
       </c>
       <c r="B8" t="n">
-        <v>97981</v>
+        <v>97998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121353620</v>
+        <v>121353622</v>
       </c>
       <c r="B9" t="n">
-        <v>97988</v>
+        <v>97094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353608</v>
+        <v>121357128</v>
       </c>
       <c r="B4" t="n">
         <v>97991</v>
@@ -929,17 +929,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R4" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,17 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121357128</v>
+        <v>121353620</v>
       </c>
       <c r="B5" t="n">
-        <v>97991</v>
+        <v>97998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R5" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353597</v>
+        <v>121353608</v>
       </c>
       <c r="B6" t="n">
-        <v>105171</v>
+        <v>97991</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353557</v>
+        <v>121353604</v>
       </c>
       <c r="B7" t="n">
         <v>97035</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353620</v>
+        <v>121353597</v>
       </c>
       <c r="B8" t="n">
-        <v>97998</v>
+        <v>105171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121357128</v>
+        <v>121353604</v>
       </c>
       <c r="B4" t="n">
-        <v>97991</v>
+        <v>97048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,37 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R4" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,17 +963,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353620</v>
+        <v>121353608</v>
       </c>
       <c r="B5" t="n">
-        <v>97998</v>
+        <v>98004</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>223572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353608</v>
+        <v>121353620</v>
       </c>
       <c r="B6" t="n">
-        <v>97991</v>
+        <v>98011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353604</v>
+        <v>121357128</v>
       </c>
       <c r="B7" t="n">
-        <v>97035</v>
+        <v>98004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>223572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R7" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,7 +1324,7 @@
         <v>121353597</v>
       </c>
       <c r="B8" t="n">
-        <v>105171</v>
+        <v>105184</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>121353622</v>
       </c>
       <c r="B9" t="n">
-        <v>97094</v>
+        <v>97107</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353604</v>
+        <v>121353597</v>
       </c>
       <c r="B4" t="n">
-        <v>97048</v>
+        <v>105185</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353608</v>
+        <v>121357128</v>
       </c>
       <c r="B5" t="n">
-        <v>98004</v>
+        <v>98005</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,17 +1036,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R5" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353620</v>
+        <v>121353622</v>
       </c>
       <c r="B6" t="n">
-        <v>98011</v>
+        <v>97108</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121357128</v>
+        <v>121353608</v>
       </c>
       <c r="B7" t="n">
-        <v>98004</v>
+        <v>98005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,17 +1250,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R7" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353597</v>
+        <v>121353557</v>
       </c>
       <c r="B8" t="n">
-        <v>105184</v>
+        <v>97049</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121353622</v>
+        <v>121353620</v>
       </c>
       <c r="B9" t="n">
-        <v>97107</v>
+        <v>98012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221063</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353597</v>
+        <v>121353557</v>
       </c>
       <c r="B4" t="n">
-        <v>105185</v>
+        <v>97052</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
         <v>121357128</v>
       </c>
       <c r="B5" t="n">
-        <v>98005</v>
+        <v>98008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>121353622</v>
       </c>
       <c r="B6" t="n">
-        <v>97108</v>
+        <v>97111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>121353608</v>
       </c>
       <c r="B7" t="n">
-        <v>98005</v>
+        <v>98008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353557</v>
+        <v>121353620</v>
       </c>
       <c r="B8" t="n">
-        <v>97049</v>
+        <v>98015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121353620</v>
+        <v>121353597</v>
       </c>
       <c r="B9" t="n">
-        <v>98012</v>
+        <v>105188</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353557</v>
+        <v>121353608</v>
       </c>
       <c r="B4" t="n">
-        <v>97052</v>
+        <v>98008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>223572</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121357128</v>
+        <v>121353604</v>
       </c>
       <c r="B5" t="n">
-        <v>98008</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,37 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R5" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353622</v>
+        <v>121353620</v>
       </c>
       <c r="B6" t="n">
-        <v>97111</v>
+        <v>98015</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221063</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353608</v>
+        <v>121353622</v>
       </c>
       <c r="B7" t="n">
-        <v>98008</v>
+        <v>97111</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223572</v>
+        <v>221063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353620</v>
+        <v>121353597</v>
       </c>
       <c r="B8" t="n">
-        <v>98015</v>
+        <v>105188</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121353597</v>
+        <v>121357128</v>
       </c>
       <c r="B9" t="n">
-        <v>105188</v>
+        <v>98008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,37 +1444,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R9" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353608</v>
+        <v>121353622</v>
       </c>
       <c r="B4" t="n">
-        <v>98008</v>
+        <v>97117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223572</v>
+        <v>221063</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353604</v>
+        <v>121353597</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>105194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353620</v>
+        <v>121353557</v>
       </c>
       <c r="B6" t="n">
-        <v>98015</v>
+        <v>97058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353622</v>
+        <v>121357128</v>
       </c>
       <c r="B7" t="n">
-        <v>97111</v>
+        <v>98014</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221063</v>
+        <v>223572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R7" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353597</v>
+        <v>121353608</v>
       </c>
       <c r="B8" t="n">
-        <v>105188</v>
+        <v>98014</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121357128</v>
+        <v>121353620</v>
       </c>
       <c r="B9" t="n">
-        <v>98008</v>
+        <v>98021</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,37 +1444,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R9" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353622</v>
+        <v>121353608</v>
       </c>
       <c r="B4" t="n">
-        <v>97117</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221063</v>
+        <v>223572</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
         <v>121353597</v>
       </c>
       <c r="B5" t="n">
-        <v>105194</v>
+        <v>105195</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>121353557</v>
       </c>
       <c r="B6" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>121357128</v>
       </c>
       <c r="B7" t="n">
-        <v>98014</v>
+        <v>98015</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353608</v>
+        <v>121353622</v>
       </c>
       <c r="B8" t="n">
-        <v>98014</v>
+        <v>97118</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223572</v>
+        <v>221063</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
         <v>121353620</v>
       </c>
       <c r="B9" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353608</v>
+        <v>121353557</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353597</v>
+        <v>121353608</v>
       </c>
       <c r="B5" t="n">
-        <v>105195</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353557</v>
+        <v>121357128</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>98015</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,37 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>223572</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R6" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121357128</v>
+        <v>121353597</v>
       </c>
       <c r="B7" t="n">
-        <v>98015</v>
+        <v>105195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223572</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R7" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353622</v>
+        <v>121353620</v>
       </c>
       <c r="B8" t="n">
-        <v>97118</v>
+        <v>98022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221063</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121353620</v>
+        <v>121353622</v>
       </c>
       <c r="B9" t="n">
-        <v>98022</v>
+        <v>97118</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353608</v>
+        <v>121353620</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353597</v>
+        <v>121353608</v>
       </c>
       <c r="B7" t="n">
-        <v>105195</v>
+        <v>98015</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353620</v>
+        <v>121353597</v>
       </c>
       <c r="B8" t="n">
-        <v>98022</v>
+        <v>105195</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353557</v>
+        <v>121353608</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>98015</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>223572</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353620</v>
+        <v>121353604</v>
       </c>
       <c r="B5" t="n">
-        <v>98022</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121357128</v>
+        <v>121353620</v>
       </c>
       <c r="B6" t="n">
-        <v>98015</v>
+        <v>98022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,37 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353608</v>
+        <v>121353622</v>
       </c>
       <c r="B7" t="n">
-        <v>98015</v>
+        <v>97118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223572</v>
+        <v>221063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121353597</v>
+        <v>121357128</v>
       </c>
       <c r="B8" t="n">
-        <v>105195</v>
+        <v>98015</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,37 +1337,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>223572</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R8" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121353622</v>
+        <v>121353597</v>
       </c>
       <c r="B9" t="n">
-        <v>97118</v>
+        <v>105195</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221063</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121353608</v>
+        <v>121353620</v>
       </c>
       <c r="B4" t="n">
-        <v>98015</v>
+        <v>98030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223572</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121353604</v>
+        <v>121353608</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>98023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>223572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353620</v>
+        <v>121353622</v>
       </c>
       <c r="B6" t="n">
-        <v>98022</v>
+        <v>97126</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353622</v>
+        <v>121357128</v>
       </c>
       <c r="B7" t="n">
-        <v>97118</v>
+        <v>98023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221063</v>
+        <v>223572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R7" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121357128</v>
+        <v>121353557</v>
       </c>
       <c r="B8" t="n">
-        <v>98015</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,37 +1337,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223572</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R8" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,7 +1431,7 @@
         <v>121353597</v>
       </c>
       <c r="B9" t="n">
-        <v>105195</v>
+        <v>105203</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121353622</v>
+        <v>121357128</v>
       </c>
       <c r="B6" t="n">
-        <v>97126</v>
+        <v>98023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,37 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221063</v>
+        <v>223572</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R6" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121357128</v>
+        <v>121353622</v>
       </c>
       <c r="B7" t="n">
-        <v>98023</v>
+        <v>97126</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223572</v>
+        <v>221063</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R7" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54547-2021 artfynd.xlsx
+++ b/artfynd/A 54547-2021 artfynd.xlsx
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121357128</v>
+        <v>121353622</v>
       </c>
       <c r="B6" t="n">
-        <v>98023</v>
+        <v>97126</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,37 +1123,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223572</v>
+        <v>221063</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodnycklar</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. cruenta</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(O F.Müll.) Hyl.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464205</v>
+        <v>464073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024097</v>
+        <v>7024130</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1991-07-12</t>
+          <t>1999-08-12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Myr, sumpskog</t>
+          <t>Sumpskog, myr</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121353622</v>
+        <v>121357128</v>
       </c>
       <c r="B7" t="n">
-        <v>97126</v>
+        <v>98023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,37 +1230,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221063</v>
+        <v>223572</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Blodnycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Dactylorhiza incarnata var. cruenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(O F.Müll.) Hyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Smedsåstjärnens S-spets, 150 m N om, Jmt</t>
+          <t>Smedsåstjärnens S-spets, 150 m ONO om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464073</v>
+        <v>464205</v>
       </c>
       <c r="R7" t="n">
-        <v>7024130</v>
+        <v>7024097</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1284,17 +1284,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1999-08-12</t>
+          <t>1991-07-12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sumpskog, myr</t>
+          <t>Myr, sumpskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
